--- a/config/默认配置/1.逐笔统计系统_配置.xlsx
+++ b/config/默认配置/1.逐笔统计系统_配置.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,42 +474,47 @@
           <t>错误类型</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>校验类型</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>校验指标</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>当前值</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>对比值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>差值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>规则编号</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>历史校验说明</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>审核意见</t>
         </is>
